--- a/Pythonproject.xlsx
+++ b/Pythonproject.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -11177,13 +11177,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="K6:K41 K42:K46 K47:K401">
+    <dataValidation type="list" allowBlank="1" sqref="K6:K401">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L6:L41 L42:L46 L47:L401">
+    <dataValidation type="list" allowBlank="1" sqref="L6:L401">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="M6:M41 M42:M46 M47:M401">
+    <dataValidation type="list" allowBlank="1" sqref="M6:M401">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
